--- a/ig/DM_FINESS_New/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -181,7 +181,7 @@
     <t>http://hl7.org/fhir/concept-properties#status</t>
   </si>
   <si>
-    <t>Statut d'un code concept</t>
+    <t>A code that indicates the status of the concept. Typical values are active, experimental, deprecated, and retired</t>
   </si>
   <si>
     <t>deprecationDate</t>
@@ -190,7 +190,7 @@
     <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
   </si>
   <si>
-    <t>Date de dépréciation du code</t>
+    <t>The date at which a concept was deprecated. Concepts that are deprecated but not inactive can still be used, but their use is discouraged, and they should be expected to be made inactive in a future release. Property type is dateTime. Note that the status property may also be used to indicate that a concept is deprecated</t>
   </si>
   <si>
     <t>retirementDate</t>
@@ -199,7 +199,7 @@
     <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
   </si>
   <si>
-    <t>Date de retrait du code</t>
+    <t>The date at which a concept was retired</t>
   </si>
   <si>
     <t>natureActivite</t>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07</t>
+    <t>2025-11-07T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
